--- a/Excel/Enterprises/Enterprise_AllEnterprises_Template_WIP_v01.xlsx
+++ b/Excel/Enterprises/Enterprise_AllEnterprises_Template_WIP_v01.xlsx
@@ -609,9 +609,9 @@
   <si>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t xml:space="preserve">← </t>
@@ -619,9 +619,9 @@
     <r>
       <rPr>
         <i/>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>DD/MM/YYYY or DD Month YYYY</t>
@@ -630,9 +630,9 @@
   <si>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t xml:space="preserve">← </t>
@@ -640,9 +640,9 @@
     <r>
       <rPr>
         <i/>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>Automatically calculated, 12 months after start date</t>
@@ -666,9 +666,9 @@
   <si>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t xml:space="preserve">← </t>
@@ -676,9 +676,9 @@
     <r>
       <rPr>
         <i/>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>Please select</t>
@@ -1295,108 +1295,106 @@
   </numFmts>
   <fonts count="55" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <i/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.14999847407452621"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.14999847407452621"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="18"/>
       <color rgb="FF183C1B"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF183C1B"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.14996795556505021"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="18"/>
       <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF533001"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
       <strike/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
       <i/>
       <strike/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
@@ -1407,219 +1405,217 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="14"/>
       <color theme="0"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1" tint="0.249977111117893"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF008000"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1" tint="0.499984740745262"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0" tint="-4.9989318521683403E-2"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1" tint="0.14996795556505021"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1" tint="0.24994659260841701"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFC44340"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF008000"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0070C0"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="12"/>
-      <color theme="0"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="0" tint="-4.9989318521683403E-2"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="1" tint="0.14996795556505021"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFC44340"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF008000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF0070C0"/>
-      <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Times New Roman"/>
+      <sz val="10"/>
+      <color rgb="FFCC6600"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="0" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <u/>
+      <sz val="9"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="0" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <i/>
+      <sz val="9"/>
+      <color theme="6" tint="-0.499984740745262"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <i/>
+      <sz val="9"/>
+      <color theme="5" tint="-0.499984740745262"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1" tint="0.24994659260841701"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="10"/>
-      <color theme="6" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <color theme="5" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Times New Roman"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
+      <sz val="9"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color rgb="FF0070C0"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1" tint="0.249977111117893"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.249977111117893"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.249977111117893"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF242424"/>
       <name val="Consolas"/>
       <family val="3"/>
@@ -1627,34 +1623,34 @@
     <font>
       <sz val="9"/>
       <color rgb="FF404040"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="14"/>
       <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="16"/>
+      <sz val="14"/>
       <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="18"/>
       <color rgb="FF0C769E"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="16"/>
+      <sz val="14"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
   </fonts>
@@ -2507,11 +2503,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2531,11 +2526,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2555,11 +2549,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2579,11 +2572,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2603,11 +2595,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2627,11 +2618,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2651,11 +2641,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2675,11 +2664,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2699,11 +2687,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2723,11 +2710,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2747,11 +2733,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2771,11 +2756,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2795,11 +2779,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2819,11 +2802,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2843,11 +2825,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2867,11 +2848,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2891,11 +2871,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2915,11 +2894,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2939,11 +2917,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2963,11 +2940,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2987,11 +2963,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3011,11 +2986,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3035,11 +3009,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3059,11 +3032,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3083,11 +3055,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3107,11 +3078,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3131,11 +3101,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3155,11 +3124,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3179,11 +3147,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3203,11 +3170,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3227,11 +3193,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3251,11 +3216,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3275,11 +3239,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3299,11 +3262,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3323,11 +3285,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3347,11 +3308,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3371,11 +3331,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3395,11 +3354,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3419,11 +3377,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3443,11 +3400,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3467,11 +3423,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3781,7 +3736,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -4441,7 +4396,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -4676,7 +4631,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -4813,7 +4768,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -6218,24 +6173,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{6496CA75-FED4-4E21-A81D-BDC20736B7B5}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -6299,24 +6254,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{1A778010-8EF6-4986-9F7A-ED1F5F66D6A5}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -6380,24 +6335,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{7DC837A9-60D0-4FEE-9D60-F5F33C8747DB}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -6461,24 +6416,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{A1C4261C-1106-48B4-9C10-E82D60412011}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -6542,24 +6497,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{AE965B10-5BD0-44CC-8118-41596A6F15E2}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -6623,24 +6578,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{304D704D-8D75-4B25-B661-1CD4BF80A14D}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -6703,16 +6658,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -6778,36 +6733,36 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Including</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t> removals (</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Net emissions)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -6873,18 +6828,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 1</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -6952,7 +6907,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1600">
+            <a:rPr lang="en-AU" sz="1400">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
@@ -7070,16 +7025,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -7145,36 +7100,36 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Including</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t> removals (</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Net emissions)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -7240,18 +7195,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 2</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -7419,16 +7374,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
@@ -7494,36 +7449,36 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Including</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t> removals (</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Net emissions)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
@@ -7589,18 +7544,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 1</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -7662,7 +7617,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -7686,7 +7641,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -7754,7 +7709,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1600">
+            <a:rPr lang="en-AU" sz="1400">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
@@ -7877,16 +7832,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
@@ -7952,36 +7907,36 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Including</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t> removals (</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Net emissions)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
@@ -8047,18 +8002,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 2</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -8230,7 +8185,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -8254,7 +8209,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -8316,7 +8271,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -8340,7 +8295,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -8402,7 +8357,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -8426,7 +8381,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -8488,7 +8443,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -8512,7 +8467,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -8574,7 +8529,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -8598,7 +8553,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -8660,7 +8615,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -8684,7 +8639,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -8746,7 +8701,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -8770,7 +8725,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -8839,24 +8794,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{325659CC-BF18-4027-9C39-6B59F0E2F578}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -8920,24 +8875,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{A9E71E38-28CF-40B4-A787-CD2A933BF092}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -9001,24 +8956,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{FBAAA7CE-3F73-42A7-B887-E644937F7159}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -9082,24 +9037,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{E266E2BA-6A96-4903-9E52-5C6BCFEF9FF1}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -9163,24 +9118,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{F8F36783-2D83-448C-9BE3-D1653ADA37CE}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -9244,24 +9199,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{9792A2EE-0599-40C6-BEC6-FB928C51F2CA}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -9325,24 +9280,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{9FBD39D1-A40C-4D41-815F-1614BABEEB25}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -9406,24 +9361,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{48E1D669-5050-474F-B029-B219812AC417}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -9486,16 +9441,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -9561,36 +9516,36 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Including</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t> removals (</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Net emissions)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -9656,18 +9611,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 1</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -9735,7 +9690,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1600">
+            <a:rPr lang="en-AU" sz="1400">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
@@ -9853,16 +9808,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -9928,36 +9883,36 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Including</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t> removals (</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Net emissions)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -10023,18 +9978,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 2</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -10202,16 +10157,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
@@ -10277,36 +10232,36 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Including</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t> removals (</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Net emissions)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
@@ -10372,18 +10327,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 1</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -10445,7 +10400,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -10469,7 +10424,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -10537,7 +10492,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1600">
+            <a:rPr lang="en-AU" sz="1400">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
@@ -10660,16 +10615,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
@@ -10735,18 +10690,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 2</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -10918,7 +10873,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -10942,7 +10897,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -11004,7 +10959,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -11028,7 +10983,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -11090,7 +11045,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -11114,7 +11069,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -11176,7 +11131,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -11200,7 +11155,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -11262,7 +11217,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -11286,7 +11241,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -11348,7 +11303,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -11372,7 +11327,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -11434,7 +11389,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -11458,7 +11413,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -11527,24 +11482,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{B945A79A-D657-45FF-8794-B3F7FE79A7B2}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -11608,24 +11563,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{A0887E06-5564-4610-905A-7D5E4A0E50F4}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -11688,7 +11643,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="2000"/>
+            <a:rPr lang="en-AU" sz="1800"/>
             <a:t>Grain sold</a:t>
           </a:r>
         </a:p>
@@ -11825,7 +11780,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="2000"/>
+            <a:rPr lang="en-AU" sz="1800"/>
             <a:t>Baled hay/silage sold</a:t>
           </a:r>
         </a:p>
@@ -12707,12 +12662,12 @@
     </a:clrScheme>
     <a:fontScheme name="Custom 1">
       <a:majorFont>
-        <a:latin typeface="Times New Roman"/>
+        <a:latin typeface="Arial"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Times New Roman"/>
+        <a:latin typeface="Arial"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -12923,31 +12878,31 @@
     <tabColor rgb="FF0C769E"/>
   </sheetPr>
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25" ht="30" customHeight="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A3" s="82" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A6" s="83" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="A7" s="5" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="A8" s="5" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -12965,7 +12920,7 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:K87"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="2.7109375" customWidth="1"/>
@@ -12993,7 +12948,7 @@
       <c r="J1" s="93"/>
       <c r="K1" s="93"/>
     </row>
-    <row r="2" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -13005,7 +12960,7 @@
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
     </row>
-    <row r="3" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -13020,7 +12975,7 @@
       <c r="J3" s="94"/>
       <c r="K3" s="94"/>
     </row>
-    <row r="4" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -13030,10 +12985,10 @@
         <v>Emissions breakdown for activities running between 01 January 2025 and 31 December 2025</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
     </row>
-    <row r="6" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>1</v>
       </c>
@@ -13041,13 +12996,13 @@
         <v>272</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="str">
         <f>HYPERLINK("#'Input - Site'!A1", "Site")</f>
         <v>Site</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="str">
         <f>HYPERLINK("#'Input - Pasture Beef'!A1", "Pasture Beef")</f>
         <v>Pasture Beef</v>
@@ -13072,7 +13027,7 @@
       </c>
       <c r="J8" s="12"/>
     </row>
-    <row r="9" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="D9" s="1" t="s">
         <v>134</v>
@@ -13100,7 +13055,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>3</v>
       </c>
@@ -13130,7 +13085,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.1-2 Methane'!A1", "4.2.1.1-2 Methane")</f>
         <v>4.2.1.1-2 Methane</v>
@@ -13161,7 +13116,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.3-4 Soil direct N2O'!A1", "4.2.1.3-4 Soil direct N2O")</f>
         <v>4.2.1.3-4 Soil direct N2O</v>
@@ -13192,7 +13147,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.5-6 Soil Atmos Dep'!A1", "4.2.1.5-6 Soil atm. deposition")</f>
         <v>4.2.1.5-6 Soil atm. deposition</v>
@@ -13223,7 +13178,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.7-8 Soil leach runoff'!A1", "4.2.1.7-8 Soil leach &amp; runoff")</f>
         <v>4.2.1.7-8 Soil leach &amp; runoff</v>
@@ -13254,7 +13209,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="D15" s="1" t="s">
         <v>174</v>
@@ -13282,7 +13237,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>2</v>
       </c>
@@ -13312,7 +13267,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="str">
         <f>HYPERLINK("#'Constants - Pasture Beef'!A1", "Constants - Pasture Beef")</f>
         <v>Constants - Pasture Beef</v>
@@ -13343,7 +13298,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="str">
         <f>HYPERLINK("#'Constants - Livestock'!A1", "Constants - Livestock")</f>
         <v>Constants - Livestock</v>
@@ -13374,7 +13329,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -13405,7 +13360,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -13436,7 +13391,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="1" t="s">
         <v>141</v>
       </c>
@@ -13463,7 +13418,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
       <c r="D22" s="1" t="s">
         <v>143</v>
@@ -13491,7 +13446,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
       <c r="D23" s="1" t="s">
         <v>144</v>
@@ -13519,7 +13474,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
       <c r="D24" s="1" t="s">
         <v>145</v>
@@ -13547,7 +13502,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D25" s="1" t="s">
         <v>146</v>
       </c>
@@ -13574,7 +13529,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="1" t="s">
         <v>147</v>
       </c>
@@ -13601,7 +13556,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D27" s="88" t="s">
         <v>5</v>
       </c>
@@ -13620,15 +13575,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D30" s="80" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D32" s="12" t="s">
         <v>274</v>
       </c>
@@ -13649,7 +13604,7 @@
       </c>
       <c r="J32" s="12"/>
     </row>
-    <row r="33" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D33" s="1" t="e" cm="1">
         <f t="array" ref="D33">"14.1.1-2 Purchased electricity " &amp; IF(X_Cell_Electricity_CalculationMethod="Location-based (simpler)", "(Location-based)", "(Market-based)")</f>
         <v>#NAME?</v>
@@ -13677,7 +13632,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D34" s="88" t="s">
         <v>275</v>
       </c>
@@ -13696,15 +13651,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D37" s="80" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="38" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D39" s="12" t="s">
         <v>277</v>
       </c>
@@ -13725,7 +13680,7 @@
       </c>
       <c r="J39" s="12"/>
     </row>
-    <row r="40" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D40" s="1" t="s">
         <v>278</v>
       </c>
@@ -13752,7 +13707,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D41" s="1" t="s">
         <v>279</v>
       </c>
@@ -13779,7 +13734,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D42" s="1" t="s">
         <v>280</v>
       </c>
@@ -13806,7 +13761,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D43" s="1" t="s">
         <v>281</v>
       </c>
@@ -13833,7 +13788,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D44" s="1" t="s">
         <v>282</v>
       </c>
@@ -13860,7 +13815,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D45" s="1" t="s">
         <v>283</v>
       </c>
@@ -13887,7 +13842,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D46" s="1" t="s">
         <v>284</v>
       </c>
@@ -13914,7 +13869,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D47" s="1" t="e" cm="1">
         <f t="array" ref="D47">"15.12.1.1 Purchased electricity " &amp; IF(X_Cell_Electricity_CalculationMethod="Location-based (simpler)", "(Location-based)", "(Market-based)")</f>
         <v>#NAME?</v>
@@ -13942,7 +13897,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D48" s="1" t="s">
         <v>285</v>
       </c>
@@ -13969,7 +13924,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D49" s="1" t="s">
         <v>286</v>
       </c>
@@ -13996,7 +13951,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D50" s="1" t="s">
         <v>287</v>
       </c>
@@ -14023,7 +13978,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D51" s="88" t="s">
         <v>288</v>
       </c>
@@ -14042,16 +13997,16 @@
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D54" s="80" t="str">
         <f>"Carbon removals from plantings for the activity period " &amp; TEXT(X_Cell_Site_StartDate, "d mmmm yyyy") &amp; " and " &amp; TEXT(X_Cell_Site_EndDate, "d mmmm yyyy")</f>
         <v>Carbon removals from plantings for the activity period 1 January 2025 and 31 December 2025</v>
       </c>
     </row>
-    <row r="55" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D56" s="88" t="s">
         <v>289</v>
       </c>
@@ -14063,16 +14018,16 @@
         <v>128</v>
       </c>
     </row>
-    <row r="57" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D59" s="80" t="str">
         <f>"Net emissions for the activity period " &amp; TEXT(X_Cell_Site_StartDate, "d mmmm yyyy") &amp; " and " &amp; TEXT(X_Cell_Site_EndDate, "d mmmm yyyy")</f>
         <v>Net emissions for the activity period 1 January 2025 and 31 December 2025</v>
       </c>
     </row>
-    <row r="60" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D61" s="12"/>
       <c r="E61" s="12" t="s">
         <v>131</v>
@@ -14082,7 +14037,7 @@
       </c>
       <c r="G61" s="12"/>
     </row>
-    <row r="62" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D62" s="97" t="s">
         <v>290</v>
       </c>
@@ -14098,7 +14053,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="63" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D63" s="97" t="s">
         <v>292</v>
       </c>
@@ -14114,30 +14069,30 @@
         <v>291</v>
       </c>
     </row>
-    <row r="64" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -14151,7 +14106,7 @@
     <tabColor rgb="FF0C769E"/>
   </sheetPr>
   <dimension ref="A1:N58"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -14161,7 +14116,7 @@
     <col min="14" max="14" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="93" customFormat="1" ht="25.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" s="93" customFormat="1" ht="30" x14ac:dyDescent="0.35" customHeight="1">
       <c r="A1" s="11" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
@@ -14169,8 +14124,8 @@
         <v>295</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25" ht="20" customHeight="1"/>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C3" s="94"/>
       <c r="D3" s="94"/>
       <c r="E3" s="94"/>
@@ -14184,13 +14139,13 @@
       <c r="M3" s="94"/>
       <c r="N3" s="94"/>
     </row>
-    <row r="32" spans="4:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="4:4" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D32" s="2" t="str">
         <f>"Emissions for whole production cycle running between " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeStart, "d mmmm yyyy") &amp; " and " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeEnd, "d mmmm yyyy")</f>
         <v>Emissions for whole production cycle running between 1 November 2025 and 31 March 2026</v>
       </c>
     </row>
-    <row r="35" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D35" s="12"/>
       <c r="E35" s="12" t="s">
         <v>131</v>
@@ -14200,7 +14155,7 @@
       </c>
       <c r="G35" s="12"/>
     </row>
-    <row r="36" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D36" s="78" t="s">
         <v>293</v>
       </c>
@@ -14216,7 +14171,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D37" s="78" t="s">
         <v>294</v>
       </c>
@@ -14232,18 +14187,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="4:10" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="4:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D39" s="2" t="str">
         <f>"Product emissions intensity for whole production cycle running between " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeStart, "d mmmm yyyy") &amp; " and " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeEnd, "d mmmm yyyy")</f>
         <v>Product emissions intensity for whole production cycle running between 1 November 2025 and 31 March 2026</v>
       </c>
     </row>
-    <row r="42" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D42" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="43" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D43" s="12" t="s">
         <v>133</v>
       </c>
@@ -14266,7 +14221,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="44" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D44" s="1" t="s">
         <v>169</v>
       </c>
@@ -14293,7 +14248,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="45" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D45" s="1" t="s">
         <v>170</v>
       </c>
@@ -14320,7 +14275,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="46" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D46" s="1" t="s">
         <v>159</v>
       </c>
@@ -14342,7 +14297,7 @@
       </c>
       <c r="J46" s="10"/>
     </row>
-    <row r="47" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D47" s="1" t="s">
         <v>171</v>
       </c>
@@ -14369,7 +14324,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="48" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D48" s="1" t="s">
         <v>172</v>
       </c>
@@ -14396,7 +14351,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="49" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D49" s="1" t="s">
         <v>160</v>
       </c>
@@ -14418,12 +14373,12 @@
       </c>
       <c r="J49" s="10"/>
     </row>
-    <row r="51" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D51" s="1" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="52" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D52" s="12" t="s">
         <v>133</v>
       </c>
@@ -14446,7 +14401,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="53" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D53" s="1" t="s">
         <v>169</v>
       </c>
@@ -14473,7 +14428,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="54" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D54" s="1" t="s">
         <v>170</v>
       </c>
@@ -14500,7 +14455,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="55" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D55" s="1" t="s">
         <v>159</v>
       </c>
@@ -14522,7 +14477,7 @@
       </c>
       <c r="J55" s="10"/>
     </row>
-    <row r="56" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D56" s="1" t="s">
         <v>171</v>
       </c>
@@ -14549,7 +14504,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="57" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D57" s="1" t="s">
         <v>172</v>
       </c>
@@ -14576,7 +14531,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D58" s="1" t="s">
         <v>160</v>
       </c>
@@ -14611,7 +14566,7 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:AA115"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="4" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" style="23" customWidth="1"/>
@@ -14632,7 +14587,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:24" s="23" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="23" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -14643,7 +14598,7 @@
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -14670,7 +14625,7 @@
       <c r="W3" s="25"/>
       <c r="X3" s="25"/>
     </row>
-    <row r="4" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -14685,19 +14640,19 @@
       <c r="J4" s="31"/>
       <c r="K4" s="31"/>
     </row>
-    <row r="5" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D5" s="2" t="s">
         <v>96</v>
       </c>
       <c r="N5" s="32"/>
     </row>
-    <row r="6" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>1</v>
       </c>
       <c r="N6" s="34"/>
     </row>
-    <row r="7" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="str">
         <f>HYPERLINK("#'Input - Site'!A1", "Site")</f>
         <v>Site</v>
@@ -14709,7 +14664,7 @@
       <c r="F7" s="45"/>
       <c r="G7" s="46"/>
     </row>
-    <row r="8" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="str">
         <f>HYPERLINK("#'Input - Pasture Beef'!A1", "Pasture Beef")</f>
         <v>Pasture Beef</v>
@@ -14721,14 +14676,14 @@
       <c r="F8" s="48"/>
       <c r="G8" s="49"/>
     </row>
-    <row r="9" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="D9" s="1"/>
       <c r="E9" s="50"/>
       <c r="F9" s="17"/>
       <c r="N9" s="36"/>
     </row>
-    <row r="10" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>3</v>
       </c>
@@ -14743,7 +14698,7 @@
       </c>
       <c r="N10" s="36"/>
     </row>
-    <row r="11" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.1-2 Methane'!A1", "4.2.1.1-2 Methane")</f>
         <v>4.2.1.1-2 Methane</v>
@@ -14760,7 +14715,7 @@
       <c r="G11" s="1"/>
       <c r="N11" s="41"/>
     </row>
-    <row r="12" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.3-4 Soil direct N2O'!A1", "4.2.1.3-4 Soil direct N2O")</f>
         <v>4.2.1.3-4 Soil direct N2O</v>
@@ -14775,7 +14730,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.5-6 Soil Atmos Dep'!A1", "4.2.1.5-6 Soil atm. deposition")</f>
         <v>4.2.1.5-6 Soil atm. deposition</v>
@@ -14792,7 +14747,7 @@
       <c r="N13" s="43"/>
       <c r="O13" s="43"/>
     </row>
-    <row r="14" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.7-8 Soil leach runoff'!A1", "4.2.1.7-8 Soil leach &amp; runoff")</f>
         <v>4.2.1.7-8 Soil leach &amp; runoff</v>
@@ -14809,7 +14764,7 @@
       <c r="N14" s="43"/>
       <c r="O14" s="43"/>
     </row>
-    <row r="15" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="D15" s="1" t="s">
         <v>109</v>
@@ -14823,7 +14778,7 @@
       <c r="N15" s="43"/>
       <c r="O15" s="43"/>
     </row>
-    <row r="16" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>2</v>
       </c>
@@ -14839,7 +14794,7 @@
       <c r="N16" s="43"/>
       <c r="O16" s="43"/>
     </row>
-    <row r="17" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="str">
         <f>HYPERLINK("#'Constants - Pasture Beef'!A1", "Constants - Pasture Beef")</f>
         <v>Constants - Pasture Beef</v>
@@ -14854,7 +14809,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="str">
         <f>HYPERLINK("#'Constants - Livestock'!A1", "Constants - Livestock")</f>
         <v>Constants - Livestock</v>
@@ -14868,7 +14823,7 @@
       </c>
       <c r="F18" s="17"/>
     </row>
-    <row r="19" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -14883,7 +14838,7 @@
       <c r="G19" s="51"/>
       <c r="N19" s="32"/>
     </row>
-    <row r="20" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -14899,7 +14854,7 @@
       <c r="G20" s="50"/>
       <c r="N20" s="34"/>
     </row>
-    <row r="21" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21"/>
       <c r="D21" s="1" t="s">
         <v>115</v>
@@ -14911,7 +14866,7 @@
       <c r="F21" s="1"/>
       <c r="G21" s="50"/>
     </row>
-    <row r="22" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
       <c r="D22" s="1" t="s">
         <v>69</v>
@@ -14922,29 +14877,29 @@
       </c>
       <c r="G22" s="54"/>
     </row>
-    <row r="23" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
     </row>
-    <row r="24" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
     </row>
-    <row r="25" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25"/>
       <c r="N25" s="34"/>
     </row>
-    <row r="26" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26"/>
     </row>
-    <row r="27" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27"/>
     </row>
-    <row r="28" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28"/>
     </row>
-    <row r="29" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29"/>
     </row>
-    <row r="30" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30"/>
       <c r="L30" s="52"/>
       <c r="M30" s="52"/>
@@ -14961,7 +14916,7 @@
       <c r="X30" s="52"/>
       <c r="Y30" s="52"/>
     </row>
-    <row r="31" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31"/>
       <c r="L31" s="53"/>
       <c r="M31" s="53"/>
@@ -14978,7 +14933,7 @@
       <c r="X31" s="53"/>
       <c r="Y31" s="53"/>
     </row>
-    <row r="32" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32"/>
       <c r="L32" s="53"/>
       <c r="M32" s="53"/>
@@ -14995,7 +14950,7 @@
       <c r="X32" s="53"/>
       <c r="Y32" s="53"/>
     </row>
-    <row r="33" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33"/>
       <c r="L33" s="53"/>
       <c r="M33" s="53"/>
@@ -15012,7 +14967,7 @@
       <c r="X33" s="53"/>
       <c r="Y33" s="53"/>
     </row>
-    <row r="34" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34"/>
       <c r="J34" s="55"/>
       <c r="K34" s="56"/>
@@ -15031,7 +14986,7 @@
       <c r="X34" s="53"/>
       <c r="Y34" s="53"/>
     </row>
-    <row r="35" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35"/>
       <c r="J35" s="55"/>
       <c r="K35" s="56"/>
@@ -15050,7 +15005,7 @@
       <c r="X35" s="53"/>
       <c r="Y35" s="53"/>
     </row>
-    <row r="36" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36"/>
       <c r="D36" s="57"/>
       <c r="E36" s="57"/>
@@ -15075,7 +15030,7 @@
       <c r="X36" s="53"/>
       <c r="Y36" s="53"/>
     </row>
-    <row r="37" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37"/>
       <c r="D37" s="57"/>
       <c r="E37" s="57"/>
@@ -15100,7 +15055,7 @@
       <c r="X37" s="53"/>
       <c r="Y37" s="53"/>
     </row>
-    <row r="38" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38"/>
       <c r="D38" s="57"/>
       <c r="E38" s="57"/>
@@ -15125,7 +15080,7 @@
       <c r="X38" s="53"/>
       <c r="Y38" s="53"/>
     </row>
-    <row r="39" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39"/>
       <c r="D39" s="57"/>
       <c r="E39" s="57"/>
@@ -15150,7 +15105,7 @@
       <c r="X39" s="53"/>
       <c r="Y39" s="53"/>
     </row>
-    <row r="40" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40"/>
       <c r="D40" s="60"/>
       <c r="E40" s="60"/>
@@ -15175,104 +15130,104 @@
       <c r="X40" s="63"/>
       <c r="Y40" s="63"/>
     </row>
-    <row r="41" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41"/>
     </row>
-    <row r="42" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42"/>
     </row>
-    <row r="43" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43"/>
     </row>
-    <row r="44" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D45" s="2"/>
     </row>
-    <row r="46" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D47" s="64"/>
       <c r="E47" s="64"/>
       <c r="F47" s="64"/>
       <c r="G47" s="64"/>
       <c r="H47" s="64"/>
     </row>
-    <row r="48" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D48" s="65"/>
       <c r="E48" s="65"/>
       <c r="F48" s="66"/>
       <c r="G48" s="66"/>
       <c r="H48" s="65"/>
     </row>
-    <row r="49" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D49" s="65"/>
       <c r="E49" s="65"/>
       <c r="F49" s="66"/>
       <c r="G49" s="66"/>
       <c r="H49" s="65"/>
     </row>
-    <row r="50" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D50" s="65"/>
       <c r="E50" s="65"/>
       <c r="F50" s="66"/>
       <c r="G50" s="66"/>
       <c r="H50" s="65"/>
     </row>
-    <row r="51" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D51" s="67"/>
       <c r="E51" s="68"/>
       <c r="F51" s="68"/>
       <c r="G51" s="68"/>
       <c r="H51" s="69"/>
     </row>
-    <row r="52" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G54" s="70"/>
     </row>
-    <row r="55" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D55" s="2"/>
     </row>
-    <row r="56" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D57" s="71"/>
       <c r="F57" s="72"/>
     </row>
-    <row r="58" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D58" s="1"/>
       <c r="E58" s="73"/>
     </row>
-    <row r="59" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D59" s="1"/>
       <c r="E59" s="73"/>
     </row>
-    <row r="60" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D60" s="1"/>
       <c r="E60" s="74"/>
     </row>
-    <row r="61" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D61" s="1"/>
     </row>
-    <row r="62" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D63" s="71"/>
     </row>
-    <row r="64" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D64" s="1"/>
       <c r="E64" s="73"/>
     </row>
-    <row r="65" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D65" s="1"/>
       <c r="E65" s="73"/>
     </row>
-    <row r="66" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D66" s="1"/>
       <c r="E66" s="74"/>
     </row>
-    <row r="67" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D69" s="75"/>
       <c r="E69" s="75"/>
       <c r="F69" s="75"/>
@@ -15280,7 +15235,7 @@
       <c r="H69" s="75"/>
       <c r="I69" s="75"/>
     </row>
-    <row r="70" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D70" s="75"/>
       <c r="E70" s="75"/>
       <c r="F70" s="75"/>
@@ -15288,7 +15243,7 @@
       <c r="H70" s="75"/>
       <c r="I70" s="75"/>
     </row>
-    <row r="71" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D71" s="75"/>
       <c r="E71" s="75"/>
       <c r="F71" s="75"/>
@@ -15296,7 +15251,7 @@
       <c r="H71" s="75"/>
       <c r="I71" s="75"/>
     </row>
-    <row r="72" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D72" s="75"/>
       <c r="E72" s="75"/>
       <c r="F72" s="75"/>
@@ -15304,59 +15259,59 @@
       <c r="H72" s="75"/>
       <c r="I72" s="75"/>
     </row>
-    <row r="73" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D78" s="76"/>
     </row>
-    <row r="79" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D79" s="76"/>
     </row>
-    <row r="80" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D80" s="76"/>
     </row>
-    <row r="81" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D81" s="76"/>
     </row>
-    <row r="82" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D82" s="76"/>
     </row>
-    <row r="83" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E12" xr:uid="{620909BD-05B7-4260-BB85-4888DFAEE1F3}">
@@ -15382,7 +15337,7 @@
     <tabColor rgb="FFCC6600"/>
   </sheetPr>
   <dimension ref="C1:J83"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -15393,7 +15348,7 @@
     <col min="11" max="11" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:10" ht="25.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="3:10" ht="30" x14ac:dyDescent="0.35" customHeight="1">
       <c r="C1" s="29" t="s">
         <v>148</v>
       </c>
@@ -15405,7 +15360,7 @@
       <c r="I1" s="23"/>
       <c r="J1" s="23"/>
     </row>
-    <row r="2" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -15415,7 +15370,7 @@
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" spans="3:10" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="3:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C3" s="30"/>
       <c r="D3" s="30"/>
       <c r="E3" s="30"/>
@@ -15425,7 +15380,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="5" spans="3:10" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D5" s="2" t="s">
         <v>88</v>
       </c>
@@ -15433,13 +15388,13 @@
       <c r="F5" s="26"/>
       <c r="G5" s="26"/>
     </row>
-    <row r="6" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D6" s="33"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
       <c r="G6" s="26"/>
     </row>
-    <row r="7" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D7" s="1" t="s">
         <v>89</v>
       </c>
@@ -15449,7 +15404,7 @@
       <c r="F7" s="17"/>
       <c r="G7" s="26"/>
     </row>
-    <row r="8" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D8" s="13" t="s">
         <v>91</v>
       </c>
@@ -15459,13 +15414,13 @@
       <c r="F8" s="26"/>
       <c r="G8" s="26"/>
     </row>
-    <row r="9" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D9" s="26"/>
       <c r="E9" s="26"/>
       <c r="F9" s="26"/>
       <c r="G9" s="26"/>
     </row>
-    <row r="10" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D10" s="37" t="s">
         <v>93</v>
       </c>
@@ -15473,13 +15428,13 @@
       <c r="F10" s="39"/>
       <c r="G10" s="40"/>
     </row>
-    <row r="11" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D11" s="26"/>
       <c r="E11" s="26"/>
       <c r="F11" s="26"/>
       <c r="G11" s="26"/>
     </row>
-    <row r="12" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D12" s="13" t="s">
         <v>17</v>
       </c>
@@ -15491,7 +15446,7 @@
       </c>
       <c r="G12" s="26"/>
     </row>
-    <row r="13" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D13" s="13" t="s">
         <v>18</v>
       </c>
@@ -15504,16 +15459,16 @@
       </c>
       <c r="G13" s="26"/>
     </row>
-    <row r="14" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="F14" s="26"/>
       <c r="G14" s="26"/>
     </row>
-    <row r="16" spans="3:10" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D16" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D18" s="1" t="s">
         <v>14</v>
       </c>
@@ -15524,7 +15479,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="19" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D19" s="1" t="s">
         <v>15</v>
       </c>
@@ -15535,7 +15490,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="20" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D20" s="1" t="s">
         <v>16</v>
       </c>
@@ -15547,7 +15502,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="22" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D22" s="1" t="s">
         <v>150</v>
       </c>
@@ -15559,7 +15514,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D23" s="1" t="s">
         <v>154</v>
       </c>
@@ -15570,7 +15525,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="24" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D24" s="1" t="s">
         <v>155</v>
       </c>
@@ -15581,7 +15536,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="25" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D25" s="1" t="s">
         <v>156</v>
       </c>
@@ -15593,7 +15548,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="27" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D27" s="1" t="s">
         <v>152</v>
       </c>
@@ -15605,7 +15560,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D28" s="1" t="s">
         <v>157</v>
       </c>
@@ -15616,7 +15571,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="29" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D29" s="1" t="s">
         <v>158</v>
       </c>
@@ -15627,7 +15582,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="30" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D30" s="1" t="s">
         <v>156</v>
       </c>
@@ -15639,7 +15594,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="32" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D32" s="1" t="s">
         <v>151</v>
       </c>
@@ -15650,7 +15605,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="33" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D33" s="1" t="s">
         <v>153</v>
       </c>
@@ -15661,18 +15616,18 @@
         <v>149</v>
       </c>
     </row>
-    <row r="36" spans="4:7" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:7" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D36" s="2" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="39" spans="4:7" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="4:7" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D39" s="80" t="str">
         <f>"Carbon captured from " &amp; TEXT(X_Cell_Site_StartDate, "d mmmm yyyy") &amp; " to " &amp; TEXT(X_Cell_Site_EndDate, "d, mmmm, yyyy") &amp; " from environmental plantings"</f>
         <v>Carbon captured from 1 January 2025 to 31, December, 2025 from environmental plantings</v>
       </c>
     </row>
-    <row r="41" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D41" s="21" t="s">
         <v>266</v>
       </c>
@@ -15686,7 +15641,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="42" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D42" s="35"/>
       <c r="E42" s="77"/>
       <c r="F42" s="19"/>
@@ -15695,29 +15650,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="4:7" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="4:7" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D46" s="2" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="48" spans="4:7" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="4:7" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D48" s="80" t="str">
         <f>"Gross emissions from other activity periods in the production timeframe " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeStart, "d mmmm yyyy") &amp; " to " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeEnd, "d mmmm yyyy")</f>
         <v>Gross emissions from other activity periods in the production timeframe 1 November 2025 to 31 March 2026</v>
       </c>
     </row>
-    <row r="50" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D50" s="90" t="str" cm="1">
         <f t="array" ref="D50">"There are " &amp; Common_InputFunctions.getOverlappingReportingCycles(X_Cell_Enterprise_ProductionTimeframeStart,X_Cell_Enterprise_ProductionTimeframeEnd,X_Cell_Site_StartDate) &amp; " emissions calculation periods that need to be completed before total product emissions can be determined."</f>
         <v>There are 2 emissions calculation periods that need to be completed before total product emissions can be determined.</v>
       </c>
     </row>
-    <row r="51" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D51" s="1" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="53" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D53" s="81" t="s">
         <v>116</v>
       </c>
@@ -15728,7 +15683,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D54" s="1" t="str" cm="1">
         <f t="array" ref="D54:D55">Common_InputFunctions.getOverlappingReportingPeriods(X_Cell_Enterprise_ProductionTimeframeStart,X_Cell_Enterprise_ProductionTimeframeEnd,X_Cell_Site_StartDate)</f>
         <v>01 Jan 2025 to 31 Dec 2025 (This reporting cycle)</v>
@@ -15745,7 +15700,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="55" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D55" s="1" t="str">
         <v>01 Jan 2026 to 31 Dec 2026</v>
       </c>
@@ -15761,7 +15716,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="56" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E56" s="77">
         <f>IF(ISBLANK($D56), 0, IF(ISNUMBER(SEARCH("reporting", $D56)), Result_Enterprise_Gross_Method1, "Enter value"))</f>
         <v>0</v>
@@ -15774,7 +15729,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="57" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E57" s="77">
         <f>IF(ISBLANK($D57), 0, IF(ISNUMBER(SEARCH("reporting", $D57)), Result_Enterprise_Gross_Method1, "Enter value"))</f>
         <v>0</v>
@@ -15787,7 +15742,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E58" s="77">
         <f>IF(ISBLANK($D58), 0, IF(ISNUMBER(SEARCH("reporting", $D58)), Result_Enterprise_Gross_Method1, "Enter value"))</f>
         <v>0</v>
@@ -15800,7 +15755,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D59" s="91" t="s">
         <v>129</v>
       </c>
@@ -15816,13 +15771,13 @@
         <v>8</v>
       </c>
     </row>
-    <row r="64" spans="4:7" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="4:7" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D64" s="80" t="str">
         <f>"Carbon removals from environmental plantings for whole production cycle running between " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeStart, "d mmmm yyyy") &amp; " and " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeEnd, "d mmmm yyyy")</f>
         <v>Carbon removals from environmental plantings for whole production cycle running between 1 November 2025 and 31 March 2026</v>
       </c>
     </row>
-    <row r="66" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D66" s="81" t="s">
         <v>116</v>
       </c>
@@ -15831,7 +15786,7 @@
       </c>
       <c r="F66" s="81"/>
     </row>
-    <row r="67" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D67" s="1" t="str" cm="1">
         <f t="array" ref="D67:D68">Common_InputFunctions.getOverlappingReportingPeriods(X_Cell_Enterprise_ProductionTimeframeStart,X_Cell_Enterprise_ProductionTimeframeEnd,X_Cell_Site_StartDate)</f>
         <v>01 Jan 2025 to 31 Dec 2025 (This reporting cycle)</v>
@@ -15844,7 +15799,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="68" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D68" s="1" t="str">
         <v>01 Jan 2026 to 31 Dec 2026</v>
       </c>
@@ -15856,7 +15811,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="69" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E69" s="77">
         <f>IF(ISBLANK($D69), 0, IF(ISNUMBER(SEARCH("reporting", $D69)), SUM(Table_Input_Enterprise_PlantingRemovals[Removal allocated to this enterprise]), "Enter value"))</f>
         <v>0</v>
@@ -15865,7 +15820,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="70" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E70" s="77">
         <f>IF(ISBLANK($D70), 0, IF(ISNUMBER(SEARCH("reporting", $D70)), SUM(Table_Input_Enterprise_PlantingRemovals[Removal allocated to this enterprise]), "Enter value"))</f>
         <v>0</v>
@@ -15874,7 +15829,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="71" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E71" s="77">
         <f>IF(ISBLANK($D71), 0, IF(ISNUMBER(SEARCH("reporting", $D71)), SUM(Table_Input_Enterprise_PlantingRemovals[Removal allocated to this enterprise]), "Enter value"))</f>
         <v>0</v>
@@ -15883,7 +15838,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="72" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D72" s="91" t="s">
         <v>130</v>
       </c>
@@ -15895,13 +15850,13 @@
         <v>128</v>
       </c>
     </row>
-    <row r="75" spans="4:7" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="4:7" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D75" s="80" t="str">
         <f>"Net emissions from other activity periods in the production timeframe " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeStart, "d mmmm yyyy") &amp; " to " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeEnd, "d mmmm yyyy")</f>
         <v>Net emissions from other activity periods in the production timeframe 1 November 2025 to 31 March 2026</v>
       </c>
     </row>
-    <row r="77" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D77" s="81" t="s">
         <v>116</v>
       </c>
@@ -15912,7 +15867,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="78" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D78" s="1" t="str" cm="1">
         <f t="array" ref="D78:D79">Common_InputFunctions.getOverlappingReportingPeriods(X_Cell_Enterprise_ProductionTimeframeStart,X_Cell_Enterprise_ProductionTimeframeEnd,X_Cell_Site_StartDate)</f>
         <v>01 Jan 2025 to 31 Dec 2025 (This reporting cycle)</v>
@@ -15929,7 +15884,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="79" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D79" s="1" t="str">
         <v>01 Jan 2026 to 31 Dec 2026</v>
       </c>
@@ -15945,7 +15900,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="80" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E80" s="77">
         <f t="shared" ref="E80:F80" si="1">IF(ISBLANK($D80), 0, IF(ISNUMBER(SEARCH("reporting", $D80)), E56-$E$67, "Enter value"))</f>
         <v>0</v>
@@ -15958,7 +15913,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="81" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E81" s="77">
         <f t="shared" ref="E81:F81" si="2">IF(ISBLANK($D81), 0, IF(ISNUMBER(SEARCH("reporting", $D81)), E57-$E$67, "Enter value"))</f>
         <v>0</v>
@@ -15971,7 +15926,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="82" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E82" s="77">
         <f t="shared" ref="E82:F82" si="3">IF(ISBLANK($D82), 0, IF(ISNUMBER(SEARCH("reporting", $D82)), E58-$E$67, "Enter value"))</f>
         <v>0</v>
@@ -15984,7 +15939,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="83" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D83" s="91" t="s">
         <v>129</v>
       </c>
@@ -16014,7 +15969,7 @@
     <tabColor rgb="FFCC6600"/>
   </sheetPr>
   <dimension ref="A1:K10"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -16023,7 +15978,7 @@
     <col min="11" max="11" width="4.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="11" customFormat="1" ht="25.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.35" customHeight="1">
       <c r="A1" s="11" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
@@ -16031,8 +15986,8 @@
         <v>177</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:11" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25" ht="20" customHeight="1"/>
+    <row r="3" spans="1:11" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C3" s="30"/>
       <c r="D3" s="30"/>
       <c r="E3" s="30"/>
@@ -16043,7 +15998,7 @@
       <c r="J3" s="30"/>
       <c r="K3" s="30"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D5" s="71" t="s">
         <v>182</v>
       </c>
@@ -16051,10 +16006,10 @@
       <c r="F5" s="71"/>
       <c r="G5" s="71"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="F6" s="17"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D7" s="1" t="s">
         <v>178</v>
       </c>
@@ -16063,7 +16018,7 @@
       </c>
       <c r="F7" s="17"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D8" s="1" t="s">
         <v>180</v>
       </c>
@@ -16073,7 +16028,7 @@
       </c>
       <c r="F8" s="17"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D9" s="1" t="s">
         <v>64</v>
       </c>
@@ -16082,7 +16037,7 @@
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D10" s="1" t="s">
         <v>181</v>
       </c>
@@ -16102,7 +16057,7 @@
     <tabColor rgb="FFCC6600"/>
   </sheetPr>
   <dimension ref="C1:M66"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -16115,13 +16070,13 @@
     <col min="14" max="14" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:13" s="11" customFormat="1" ht="25.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="3:13" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.35" customHeight="1">
       <c r="C1" s="11" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="2" spans="3:13" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="3:13" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:13" s="3" customFormat="1" x14ac:dyDescent="0.25" ht="20" customHeight="1"/>
+    <row r="3" spans="3:13" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C3" s="30"/>
       <c r="D3" s="30"/>
       <c r="E3" s="30"/>
@@ -16134,12 +16089,12 @@
       <c r="L3" s="30"/>
       <c r="M3" s="30"/>
     </row>
-    <row r="5" spans="3:13" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:13" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D5" s="2" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="7" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D7" s="81" t="s">
         <v>256</v>
       </c>
@@ -16162,7 +16117,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="8" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D8" s="1" t="s">
         <v>150</v>
       </c>
@@ -16182,7 +16137,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D9" s="1" t="str">
         <f>"Grain sold"</f>
         <v>Grain sold</v>
@@ -16203,7 +16158,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D10" s="1" t="str">
         <f>"Baled hay/silage produced"</f>
         <v>Baled hay/silage produced</v>
@@ -16224,7 +16179,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D11" s="1" t="str">
         <f>"Baled hay/silage sold"</f>
         <v>Baled hay/silage sold</v>
@@ -16245,7 +16200,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D12" s="1" t="str">
         <f>"Percent income from grain sold"</f>
         <v>Percent income from grain sold</v>
@@ -16266,7 +16221,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D13" s="1" t="str">
         <f>"Percent income from baled hay/silage sold"</f>
         <v>Percent income from baled hay/silage sold</v>
@@ -16287,18 +16242,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="J15" s="86">
         <f>SUM(Table_Input_DataQuality_Enterprise[Score])</f>
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="3:13" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:13" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D16" s="2" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="18" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D18" s="81" t="s">
         <v>256</v>
       </c>
@@ -16321,7 +16276,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="19" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D19" s="1" t="str">
         <f>"Leaching zone"</f>
         <v>Leaching zone</v>
@@ -16342,7 +16297,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D20" s="1" t="str">
         <f>"Elevation"</f>
         <v>Elevation</v>
@@ -16363,7 +16318,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D21" s="1" t="str">
         <f>"Average temperature for reporting period"</f>
         <v>Average temperature for reporting period</v>
@@ -16384,7 +16339,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D22" s="1" t="str">
         <f>"Total rainfall for reporting period"</f>
         <v>Total rainfall for reporting period</v>
@@ -16405,7 +16360,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D23" s="1" t="str">
         <f>"Potential evapotranspiration for reporting period"</f>
         <v>Potential evapotranspiration for reporting period</v>
@@ -16426,7 +16381,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D24" s="1" t="str">
         <f>"Number of frost days for reporting period"</f>
         <v>Number of frost days for reporting period</v>
@@ -16447,18 +16402,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="J26" s="86">
         <f>SUM(Table_Input_DataQuality_Site[Score])</f>
         <v>73</v>
       </c>
     </row>
-    <row r="27" spans="4:10" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="4:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D27" s="2" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="29" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D29" s="81" t="s">
         <v>256</v>
       </c>
@@ -16481,7 +16436,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="30" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D30" s="1" t="str">
         <f>"Crop type"</f>
         <v>Crop type</v>
@@ -16502,7 +16457,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D31" s="1" t="str">
         <f>"Irrigation method"</f>
         <v>Irrigation method</v>
@@ -16523,7 +16478,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D32" s="1" t="str">
         <f>"Area under cropping"</f>
         <v>Area under cropping</v>
@@ -16544,7 +16499,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D33" s="1" t="s">
         <v>298</v>
       </c>
@@ -16564,18 +16519,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="J35" s="86">
         <f>SUM(Table_Input_DataQuality_PastureManagement[Score])</f>
         <v>56</v>
       </c>
     </row>
-    <row r="36" spans="4:10" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D36" s="2" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="38" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D38" s="81" t="s">
         <v>256</v>
       </c>
@@ -16598,7 +16553,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="39" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D39" s="1" t="str">
         <f>"Branded inorganic fertiliser applications"</f>
         <v>Branded inorganic fertiliser applications</v>
@@ -16619,7 +16574,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D40" s="1" t="str">
         <f>"Custom inorganic fertiliser blend applications"</f>
         <v>Custom inorganic fertiliser blend applications</v>
@@ -16640,7 +16595,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D41" s="1" t="str">
         <f>"Lime applications"</f>
         <v>Lime applications</v>
@@ -16661,7 +16616,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D42" s="1" t="str">
         <f>"Organic fertiliser applications"</f>
         <v>Organic fertiliser applications</v>
@@ -16682,18 +16637,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="J44" s="86">
         <f>SUM(Table_Input_DataQuality_FertiliserApplications[Score])</f>
         <v>55</v>
       </c>
     </row>
-    <row r="45" spans="4:10" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="4:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D45" s="2" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="47" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D47" s="81" t="s">
         <v>256</v>
       </c>
@@ -16716,7 +16671,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="48" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D48" s="1" t="str">
         <f>"Fuel purchases"</f>
         <v>Fuel purchases</v>
@@ -16737,7 +16692,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D49" s="1" t="str">
         <f>"Fuel consumption"</f>
         <v>Fuel consumption</v>
@@ -16758,7 +16713,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="50" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D50" s="1" t="str">
         <f>"Electricity consumption"</f>
         <v>Electricity consumption</v>
@@ -16779,7 +16734,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="51" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D51" s="1" t="str">
         <f>"Electricity generation"</f>
         <v>Electricity generation</v>
@@ -16800,18 +16755,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="53" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="J53" s="86">
         <f>SUM(Table_Input_DataQuality_FuelElectricity[Score])</f>
         <v>55</v>
       </c>
     </row>
-    <row r="55" spans="4:10" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D55" s="2" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="57" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D57" s="81" t="s">
         <v>256</v>
       </c>
@@ -16834,7 +16789,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="58" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D58" s="1" t="str">
         <f>"Farm input purchases"</f>
         <v>Farm input purchases</v>
@@ -16855,7 +16810,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D59" s="1" t="str">
         <f>"Inbound freight use"</f>
         <v>Inbound freight use</v>
@@ -16876,7 +16831,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="60" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D60" s="1" t="str">
         <f>"Outbound freight use"</f>
         <v>Outbound freight use</v>
@@ -16897,7 +16852,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="61" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D61" s="1" t="s">
         <v>299</v>
       </c>
@@ -16911,7 +16866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D62" s="1" t="str">
         <f>"Solid waste generation and treatment"</f>
         <v>Solid waste generation and treatment</v>
@@ -16932,13 +16887,13 @@
         <v>14</v>
       </c>
     </row>
-    <row r="64" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="J64" s="86">
         <f>SUM(Table_Input_DataQuality_FarmInputsFreightWaste[Score])</f>
         <v>55</v>
       </c>
     </row>
-    <row r="66" spans="4:5" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:5" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D66" s="88" t="s">
         <v>264</v>
       </c>
@@ -16977,7 +16932,7 @@
     <tabColor theme="2" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:BY297"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="23" customWidth="1"/>
     <col min="2" max="2" width="2.7109375" style="23" customWidth="1"/>
@@ -17010,10 +16965,10 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:65" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:65" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2"/>
     </row>
-    <row r="3" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -17040,11 +16995,11 @@
       <c r="V3" s="25"/>
       <c r="W3" s="25"/>
     </row>
-    <row r="4" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4"/>
       <c r="BM4" s="26"/>
     </row>
-    <row r="5" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5"/>
       <c r="D5" s="2" t="str" cm="1">
         <f t="array" ref="D5">Common_SourceData.Common_SourceData_AustralianStatesTerritories_Title()</f>
@@ -17052,7 +17007,7 @@
       </c>
       <c r="BM5" s="26"/>
     </row>
-    <row r="6" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="83" t="s">
         <v>2</v>
       </c>
@@ -17066,7 +17021,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="84" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -17084,7 +17039,7 @@
         <v>NSW</v>
       </c>
     </row>
-    <row r="8" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -17102,7 +17057,7 @@
         <v>ACT</v>
       </c>
     </row>
-    <row r="9" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9"/>
       <c r="D9" s="21" t="str" cm="1">
         <f t="array" ref="D9">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -17117,7 +17072,7 @@
         <v>VIC</v>
       </c>
     </row>
-    <row r="10" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10"/>
       <c r="D10" s="21" t="str" cm="1">
         <f t="array" ref="D10">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -17132,7 +17087,7 @@
         <v>QLD</v>
       </c>
     </row>
-    <row r="11" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11"/>
       <c r="D11" s="21" t="str" cm="1">
         <f t="array" ref="D11">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -17148,7 +17103,7 @@
       </c>
       <c r="BM11" s="26"/>
     </row>
-    <row r="12" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12"/>
       <c r="D12" s="21" t="str" cm="1">
         <f t="array" ref="D12">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -17164,7 +17119,7 @@
       </c>
       <c r="BM12" s="26"/>
     </row>
-    <row r="13" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13"/>
       <c r="D13" s="21" t="str" cm="1">
         <f t="array" ref="D13">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -17179,7 +17134,7 @@
         <v>TAS</v>
       </c>
     </row>
-    <row r="14" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14"/>
       <c r="D14" s="21" t="str" cm="1">
         <f t="array" ref="D14">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -17194,129 +17149,129 @@
         <v>NT</v>
       </c>
     </row>
-    <row r="15" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15"/>
     </row>
-    <row r="16" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16"/>
     </row>
-    <row r="17" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17"/>
     </row>
-    <row r="18" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18"/>
       <c r="D18" s="2" t="str" cm="1">
         <f t="array" ref="D18">Common_SourceData.Common_SourceData_WASA4Areas_Title()</f>
         <v>ABS Statistcal Areas Level 4 - Western Australia</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19"/>
       <c r="D19" s="18" t="str" cm="1">
         <f t="array" ref="D19">Common_SourceData.Common_SourceData_WASA4Areas_Source()</f>
         <v>Australian Bureau of Statistics (ABS) - Statistical Areas Level 2 - 2021 - Shapefile</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20"/>
       <c r="D20" s="21" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21"/>
       <c r="D21" s="21" t="str" cm="1">
         <f t="array" ref="D21">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Bunbury</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22"/>
       <c r="D22" s="21" t="str" cm="1">
         <f t="array" ref="D22">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Mandurah</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23"/>
       <c r="D23" s="21" t="str" cm="1">
         <f t="array" ref="D23">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - Inner</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24"/>
       <c r="D24" s="21" t="str" cm="1">
         <f t="array" ref="D24">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - North East</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25"/>
       <c r="D25" s="21" t="str" cm="1">
         <f t="array" ref="D25">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - North West</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26"/>
       <c r="D26" s="21" t="str" cm="1">
         <f t="array" ref="D26">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - South East</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27"/>
       <c r="D27" s="21" t="str" cm="1">
         <f t="array" ref="D27">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - South West</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28"/>
       <c r="D28" s="21" t="str" cm="1">
         <f t="array" ref="D28">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Wheat Belt</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29"/>
       <c r="D29" s="21" t="str" cm="1">
         <f t="array" ref="D29">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Outback (North)</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30"/>
       <c r="D30" s="21" t="str" cm="1">
         <f t="array" ref="D30">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Outback (South)</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31"/>
     </row>
-    <row r="32" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32"/>
     </row>
-    <row r="33" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33"/>
     </row>
-    <row r="34" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34"/>
       <c r="D34" s="2" t="str" cm="1">
         <f t="array" ref="D34">Common_SourceData.Common_SourceData_GWP_Title()</f>
         <v>Global warming potential for greenhouse gases</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35"/>
       <c r="D35" s="18" t="str" cm="1">
         <f t="array" ref="D35">Common_SourceData.Common_SourceData_GWP_Source()</f>
         <v>XXXXXXX</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36"/>
       <c r="D36" s="21" t="s">
         <v>26</v>
@@ -17325,7 +17280,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37"/>
       <c r="D37" s="21" t="str" cm="1">
         <f t="array" ref="D37">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -17336,7 +17291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38"/>
       <c r="D38" s="21" t="str" cm="1">
         <f t="array" ref="D38">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -17347,7 +17302,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39"/>
       <c r="D39" s="21" t="str" cm="1">
         <f t="array" ref="D39">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -17358,7 +17313,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40"/>
       <c r="D40" s="21" t="str" cm="1">
         <f t="array" ref="D40">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -17369,7 +17324,7 @@
         <v>6630</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41"/>
       <c r="D41" s="21" t="str" cm="1">
         <f t="array" ref="D41">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -17380,7 +17335,7 @@
         <v>12200</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42"/>
       <c r="D42" s="21" t="str" cm="1">
         <f t="array" ref="D42">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -17391,7 +17346,7 @@
         <v>22800</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43"/>
       <c r="D43" s="21" t="str" cm="1">
         <f t="array" ref="D43">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -17402,24 +17357,24 @@
         <v>17200</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44"/>
     </row>
-    <row r="45" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45"/>
       <c r="D45" s="2" t="str" cm="1">
         <f t="array" ref="D45">Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Title()</f>
         <v>Factor to convert elemental mass of gas to molecular mass</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46"/>
       <c r="D46" s="18" t="str" cm="1">
         <f t="array" ref="D46">Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Source()</f>
         <v>XXXXXXX</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47"/>
       <c r="D47" s="21" t="s">
         <v>26</v>
@@ -17437,7 +17392,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48"/>
       <c r="D48" s="21" t="str" cm="1">
         <f t="array" ref="D48">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17460,7 +17415,7 @@
         <v>3.6666666666666665</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49"/>
       <c r="D49" s="21" t="str" cm="1">
         <f t="array" ref="D49">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17483,7 +17438,7 @@
         <v>1.3333333333333333</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50"/>
       <c r="D50" s="21" t="str" cm="1">
         <f t="array" ref="D50">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17506,7 +17461,7 @@
         <v>1.5714285714285714</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51"/>
       <c r="D51" s="21" t="str" cm="1">
         <f t="array" ref="D51">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17529,7 +17484,7 @@
         <v>3.2857142857142856</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52"/>
       <c r="D52" s="21" t="str" cm="1">
         <f t="array" ref="D52">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17552,7 +17507,7 @@
         <v>2.3333333333333335</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53"/>
       <c r="D53" s="21" t="str" cm="1">
         <f t="array" ref="D53">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17575,7 +17530,7 @@
         <v>3.6666666666666665</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54"/>
       <c r="D54" s="21" t="str" cm="1">
         <f t="array" ref="D54">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17598,49 +17553,49 @@
         <v>1.1666666666666667</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55"/>
     </row>
-    <row r="56" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56"/>
     </row>
-    <row r="57" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57"/>
       <c r="D57" s="2" t="str" cm="1">
         <f t="array" ref="D57">Common_SourceData.Common_SourceData_WetAndDryZones_Title()</f>
         <v>VEERG Australian wet and dry zones</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58"/>
       <c r="D58" s="18" t="str" cm="1">
         <f t="array" ref="D58">Common_SourceData.Common_SourceData_WetAndDryZones_Source()</f>
         <v>VEERG 2026: Table 1.2: Translating climate zones to wet and dry zones</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59"/>
       <c r="D59" s="27" t="str" cm="1">
         <f t="array" ref="D59:D61">"⚠️" &amp; Common_SourceData.Common_SourceData_WetAndDryZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60"/>
       <c r="D60" s="27" t="str">
         <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61"/>
       <c r="D61" s="27" t="str">
         <v>⚠️Fixed typo - Changed 'Fry' to 'Dry'.</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62"/>
     </row>
-    <row r="63" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63"/>
       <c r="D63" s="21" t="s">
         <v>32</v>
@@ -17649,7 +17604,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64"/>
       <c r="D64" s="21" t="str" cm="1">
         <f t="array" ref="D64">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17660,7 +17615,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65"/>
       <c r="D65" s="21" t="str" cm="1">
         <f t="array" ref="D65">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17671,7 +17626,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66"/>
       <c r="D66" s="21" t="str" cm="1">
         <f t="array" ref="D66">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17682,7 +17637,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67"/>
       <c r="D67" s="21" t="str" cm="1">
         <f t="array" ref="D67">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17693,7 +17648,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68"/>
       <c r="D68" s="21" t="str" cm="1">
         <f t="array" ref="D68">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17704,7 +17659,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69"/>
       <c r="D69" s="21" t="str" cm="1">
         <f t="array" ref="D69">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17715,7 +17670,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70"/>
       <c r="D70" s="21" t="str" cm="1">
         <f t="array" ref="D70">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17726,7 +17681,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71"/>
       <c r="D71" s="21" t="str" cm="1">
         <f t="array" ref="D71">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17737,7 +17692,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72"/>
       <c r="D72" s="21" t="str" cm="1">
         <f t="array" ref="D72">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17748,7 +17703,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73"/>
       <c r="D73" s="21" t="str" cm="1">
         <f t="array" ref="D73">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17759,7 +17714,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74"/>
       <c r="D74" s="21" t="str" cm="1">
         <f t="array" ref="D74">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17770,7 +17725,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75"/>
       <c r="D75" s="21" t="str" cm="1">
         <f t="array" ref="D75">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17781,7 +17736,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76"/>
       <c r="D76" s="21" t="str" cm="1">
         <f t="array" ref="D76">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17792,7 +17747,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77"/>
       <c r="D77" s="21" t="str" cm="1">
         <f t="array" ref="D77">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17803,64 +17758,64 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78"/>
     </row>
-    <row r="79" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79"/>
     </row>
-    <row r="80" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80"/>
     </row>
-    <row r="81" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81"/>
       <c r="D81" s="2" t="str" cm="1">
         <f t="array" ref="D81">Common_SourceData.Common_SourceData_ClimateZones_Title()</f>
         <v>VEERG Australian climate zones</v>
       </c>
     </row>
-    <row r="82" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82"/>
       <c r="D82" s="18" t="str" cm="1">
         <f t="array" ref="D82">Common_SourceData.Common_SourceData_ClimateZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="83" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83"/>
       <c r="D83" s="27" t="str" cm="1">
         <f t="array" ref="D83:D87">"⚠️" &amp; Common_SourceData.Common_SourceData_ClimateZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="84" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84"/>
       <c r="D84" s="27" t="str">
         <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
       </c>
     </row>
-    <row r="85" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85"/>
       <c r="D85" s="27" t="str">
         <v>⚠️Fixed typo in MAT value for warm temperate dry - changed 10 to 11.</v>
       </c>
     </row>
-    <row r="86" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86"/>
       <c r="D86" s="27" t="str">
         <v>⚠️Added min and max columns for MAT, MAP, frost days per year, elevation, MAP:PET to calculate zones from real climate data.</v>
       </c>
     </row>
-    <row r="87" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87"/>
       <c r="D87" s="27" t="str">
         <v>⚠️GAF accepts rainfall as a proxy for precipitation.</v>
       </c>
     </row>
-    <row r="88" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88"/>
     </row>
-    <row r="89" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89"/>
       <c r="D89" s="21" t="s">
         <v>32</v>
@@ -17912,7 +17867,7 @@
       </c>
       <c r="T89" s="21"/>
     </row>
-    <row r="90" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90"/>
       <c r="D90" s="21" t="str" cm="1">
         <f t="array" ref="D90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -17980,7 +17935,7 @@
       </c>
       <c r="T90" s="21"/>
     </row>
-    <row r="91" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91"/>
       <c r="D91" s="21" t="str" cm="1">
         <f t="array" ref="D91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -18048,7 +18003,7 @@
       </c>
       <c r="T91" s="21"/>
     </row>
-    <row r="92" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92"/>
       <c r="D92" s="21" t="str" cm="1">
         <f t="array" ref="D92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -18116,7 +18071,7 @@
       </c>
       <c r="T92" s="21"/>
     </row>
-    <row r="93" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93"/>
       <c r="D93" s="21" t="str" cm="1">
         <f t="array" ref="D93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -18184,7 +18139,7 @@
       </c>
       <c r="T93" s="21"/>
     </row>
-    <row r="94" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94"/>
       <c r="D94" s="21" t="str" cm="1">
         <f t="array" ref="D94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -18252,7 +18207,7 @@
       </c>
       <c r="T94" s="21"/>
     </row>
-    <row r="95" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95"/>
       <c r="D95" s="21" t="str" cm="1">
         <f t="array" ref="D95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -18320,7 +18275,7 @@
       </c>
       <c r="T95" s="21"/>
     </row>
-    <row r="96" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96"/>
       <c r="D96" s="21" t="str" cm="1">
         <f t="array" ref="D96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -18388,7 +18343,7 @@
       </c>
       <c r="T96" s="21"/>
     </row>
-    <row r="97" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97"/>
       <c r="D97" s="21" t="str" cm="1">
         <f t="array" ref="D97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -18456,66 +18411,66 @@
       </c>
       <c r="T97" s="21"/>
     </row>
-    <row r="98" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98"/>
     </row>
-    <row r="99" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99"/>
       <c r="D99" s="10" t="str" cm="1">
         <f t="array" ref="D99:D102">Common_SourceData.Common_SourceData_ClimateZones_Appendices()</f>
         <v>Note:</v>
       </c>
     </row>
-    <row r="100" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100"/>
       <c r="D100" s="10" t="str">
         <v>MAT = mean annual temperature</v>
       </c>
     </row>
-    <row r="101" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101"/>
       <c r="D101" s="10" t="str">
         <v>MAP = mean annual precipitation</v>
       </c>
     </row>
-    <row r="102" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102"/>
       <c r="D102" s="10" t="str">
         <v>PET = potential evapotranspiration</v>
       </c>
     </row>
-    <row r="103" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103"/>
       <c r="D103" s="10"/>
     </row>
-    <row r="104" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104"/>
     </row>
-    <row r="105" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105"/>
       <c r="D105" s="2" t="str" cm="1">
         <f t="array" ref="D105">Common_SourceData.Common_SourceData_TemperatureZones_Title()</f>
         <v>VEERG Australian temperature zones</v>
       </c>
     </row>
-    <row r="106" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106"/>
       <c r="D106" s="18" t="str" cm="1">
         <f t="array" ref="D106">Common_SourceData.Common_SourceData_TemperatureZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="107" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107"/>
       <c r="D107" s="27" t="str" cm="1">
         <f t="array" ref="D107">"⚠️" &amp; Common_SourceData.Common_SourceData_TemperatureZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA: Added extra MAT min and MAT max columns to calculate zone from real temperature data.</v>
       </c>
     </row>
-    <row r="108" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108"/>
     </row>
-    <row r="109" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109"/>
       <c r="D109" s="21" t="s">
         <v>49</v>
@@ -18530,7 +18485,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="110" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110"/>
       <c r="D110" s="21" t="str" cm="1">
         <f t="array" ref="D110">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -18549,7 +18504,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="111" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111"/>
       <c r="D111" s="21" t="str" cm="1">
         <f t="array" ref="D111">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -18568,7 +18523,7 @@
         <v>25.998999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112"/>
       <c r="D112" s="21" t="str" cm="1">
         <f t="array" ref="D112">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -18587,13 +18542,13 @@
         <v>14.999000000000001</v>
       </c>
     </row>
-    <row r="113" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113"/>
     </row>
-    <row r="114" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114"/>
     </row>
-    <row r="115" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115"/>
       <c r="D115" s="2" t="str" cm="1">
         <f t="array" ref="D115">Common_SourceData.Common_SourceData_RainfallZones_Title()</f>
@@ -18601,7 +18556,7 @@
       </c>
       <c r="BN115" s="23"/>
     </row>
-    <row r="116" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116"/>
       <c r="D116" s="18" t="str" cm="1">
         <f t="array" ref="D116">Common_SourceData.Common_SourceData_RainfallZones_Source()</f>
@@ -18609,7 +18564,7 @@
       </c>
       <c r="BN116" s="23"/>
     </row>
-    <row r="117" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117"/>
       <c r="D117" s="27" t="str" cm="1">
         <f t="array" ref="D117">"⚠️" &amp; Common_SourceData.Common_SourceData_RainfallZones_Variation()</f>
@@ -18617,11 +18572,11 @@
       </c>
       <c r="BN117" s="23"/>
     </row>
-    <row r="118" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118"/>
       <c r="BN118" s="23"/>
     </row>
-    <row r="119" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119"/>
       <c r="D119" s="21" t="s">
         <v>52</v>
@@ -18637,7 +18592,7 @@
       </c>
       <c r="BN119" s="23"/>
     </row>
-    <row r="120" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120"/>
       <c r="D120" s="21" t="str" cm="1">
         <f t="array" ref="D120">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
@@ -18657,7 +18612,7 @@
       </c>
       <c r="BN120" s="23"/>
     </row>
-    <row r="121" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121"/>
       <c r="D121" s="21" t="str" cm="1">
         <f t="array" ref="D121">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
@@ -18677,31 +18632,31 @@
       </c>
       <c r="BN121" s="23"/>
     </row>
-    <row r="122" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122"/>
       <c r="BN122" s="23"/>
     </row>
-    <row r="123" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123"/>
     </row>
-    <row r="124" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124"/>
       <c r="D124" s="2" t="str" cm="1">
         <f t="array" ref="D124">Common_SourceData.Common_SourceData_LeachingZones_Title()</f>
         <v>VEERG Australian leaching zones</v>
       </c>
     </row>
-    <row r="125" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125"/>
       <c r="D125" s="18" t="str" cm="1">
         <f t="array" ref="D125">Common_SourceData.Common_SourceData_LeachingZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="126" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126"/>
     </row>
-    <row r="127" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127"/>
       <c r="D127" s="21" t="s">
         <v>54</v>
@@ -18710,7 +18665,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="128" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128"/>
       <c r="D128" s="21" t="str" cm="1">
         <f t="array" ref="D128">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
@@ -18721,7 +18676,7 @@
         <v>Σ(𝑟𝑎𝑖𝑛)&gt;Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦</v>
       </c>
     </row>
-    <row r="129" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129"/>
       <c r="D129" s="21" t="str" cm="1">
         <f t="array" ref="D129">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
@@ -18732,13 +18687,13 @@
         <v>Σ(𝑟𝑎𝑖𝑛)≤Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦</v>
       </c>
     </row>
-    <row r="130" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130"/>
     </row>
-    <row r="131" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131"/>
     </row>
-    <row r="132" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132"/>
       <c r="D132" s="2" t="str" cm="1">
         <f t="array" ref="D132">Common_SourceData.Common_SourceData_FracWET_Title()</f>
@@ -18746,7 +18701,7 @@
       </c>
       <c r="E132" s="9"/>
     </row>
-    <row r="133" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133"/>
       <c r="D133" s="18" t="str" cm="1">
         <f t="array" ref="D133">Common_SourceData.Common_SourceData_FracWET_Source()</f>
@@ -18754,7 +18709,7 @@
       </c>
       <c r="E133" s="9"/>
     </row>
-    <row r="134" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134"/>
       <c r="D134" t="s">
         <v>56</v>
@@ -18763,7 +18718,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="135" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135"/>
       <c r="D135" t="str" cm="1">
         <f t="array" ref="D135">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
@@ -18774,7 +18729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136"/>
       <c r="D136" s="1" t="str" cm="1">
         <f t="array" ref="D136">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
@@ -18785,10 +18740,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137"/>
     </row>
-    <row r="138" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138"/>
       <c r="BN138" s="23"/>
       <c r="BO138" s="23"/>
@@ -18803,7 +18758,7 @@
       <c r="BX138" s="23"/>
       <c r="BY138" s="23"/>
     </row>
-    <row r="139" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139"/>
       <c r="D139" s="2" t="str" cm="1">
         <f t="array" ref="D139">Common_SourceData.Common_SourceData_FracWETIrrigation_Title()</f>
@@ -18822,7 +18777,7 @@
       <c r="BX139" s="23"/>
       <c r="BY139" s="23"/>
     </row>
-    <row r="140" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140"/>
       <c r="D140" s="18" t="str" cm="1">
         <f t="array" ref="D140">Common_SourceData.Common_SourceData_FracWETIrrigation_Source()</f>
@@ -18841,7 +18796,7 @@
       <c r="BX140" s="23"/>
       <c r="BY140" s="23"/>
     </row>
-    <row r="141" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141"/>
       <c r="D141" s="27" t="str" cm="1">
         <f t="array" ref="D141">Common_SourceData.Common_SourceData_FracWETIrrigation_Variation()</f>
@@ -18849,7 +18804,7 @@
       </c>
       <c r="BN141" s="23"/>
     </row>
-    <row r="142" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142"/>
       <c r="D142" s="21" t="s">
         <v>58</v>
@@ -18859,7 +18814,7 @@
       </c>
       <c r="BN142" s="23"/>
     </row>
-    <row r="143" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143"/>
       <c r="D143" s="21" t="str" cm="1">
         <f t="array" ref="D143">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -18871,7 +18826,7 @@
       </c>
       <c r="BN143" s="23"/>
     </row>
-    <row r="144" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144"/>
       <c r="D144" s="1" t="str" cm="1">
         <f t="array" ref="D144">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -18883,7 +18838,7 @@
       </c>
       <c r="BN144" s="23"/>
     </row>
-    <row r="145" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145"/>
       <c r="D145" s="1" t="str" cm="1">
         <f t="array" ref="D145">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -18895,7 +18850,7 @@
       </c>
       <c r="BN145" s="23"/>
     </row>
-    <row r="146" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146"/>
       <c r="D146" s="1" t="str" cm="1">
         <f t="array" ref="D146">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -18907,7 +18862,7 @@
       </c>
       <c r="BN146" s="23"/>
     </row>
-    <row r="147" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147"/>
       <c r="D147" s="1" t="str" cm="1">
         <f t="array" ref="D147">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -18919,15 +18874,15 @@
       </c>
       <c r="BN147" s="23"/>
     </row>
-    <row r="148" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148"/>
       <c r="BN148" s="23"/>
     </row>
-    <row r="149" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149"/>
       <c r="BN149" s="23"/>
     </row>
-    <row r="150" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150"/>
       <c r="D150" s="2" t="str" cm="1">
         <f t="array" ref="D150">Common_SourceData.Common_SourceData_DataScores_Scope3_Title()</f>
@@ -18935,7 +18890,7 @@
       </c>
       <c r="BN150" s="23"/>
     </row>
-    <row r="151" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151"/>
       <c r="D151" s="18" t="str" cm="1">
         <f t="array" ref="D151">Common_SourceData.Common_SourceData_DataScores_Scope3_Source()</f>
@@ -18943,11 +18898,11 @@
       </c>
       <c r="BN151" s="23"/>
     </row>
-    <row r="152" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152"/>
       <c r="BN152" s="23"/>
     </row>
-    <row r="153" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153"/>
       <c r="D153" s="21" t="s">
         <v>59</v>
@@ -18967,7 +18922,7 @@
       <c r="BL153" s="26"/>
       <c r="BM153" s="26"/>
     </row>
-    <row r="154" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154"/>
       <c r="D154" s="21" t="str" cm="1">
         <f t="array" ref="D154">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -18989,7 +18944,7 @@
       <c r="BL154" s="26"/>
       <c r="BM154" s="26"/>
     </row>
-    <row r="155" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155"/>
       <c r="D155" s="21" t="str" cm="1">
         <f t="array" ref="D155">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -19011,7 +18966,7 @@
       <c r="BL155" s="26"/>
       <c r="BM155" s="26"/>
     </row>
-    <row r="156" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156"/>
       <c r="D156" s="21" t="str" cm="1">
         <f t="array" ref="D156">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -19022,7 +18977,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="157" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157"/>
       <c r="D157" s="21" t="str" cm="1">
         <f t="array" ref="D157">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -19033,7 +18988,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="158" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158"/>
       <c r="D158" s="21" t="str" cm="1">
         <f t="array" ref="D158">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -19044,34 +18999,34 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159"/>
     </row>
-    <row r="160" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160"/>
     </row>
-    <row r="161" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D161" s="2" t="str" cm="1">
         <f t="array" ref="D161">Common_SourceData.Common_SourceData_FracLEACH_Title()</f>
         <v>Fraction of N that is available for leaching and runoff</v>
       </c>
       <c r="E161" s="9"/>
     </row>
-    <row r="162" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D162" s="18" t="str" cm="1">
         <f t="array" ref="D162">Common_SourceData.Common_SourceData_FracLEACH_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
       </c>
       <c r="E162" s="9"/>
     </row>
-    <row r="163" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D163" s="18" t="str" cm="1">
         <f t="array" ref="D163">Common_SourceData.Common_SourceData_FracLEACH_NIRReference()</f>
         <v>National Inventory Report Volume 1: Leaching and runoff (3.D.b.2)</v>
       </c>
       <c r="E163" s="9"/>
     </row>
-    <row r="164" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D164" s="9" t="str" cm="1">
         <f t="array" ref="D164:E164">Common_SourceData.Common_SourceData_FracLEACH_Data()</f>
         <v>FracLEACH</v>
@@ -19080,17 +19035,17 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="165" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN165" s="23"/>
       <c r="BO165" s="23"/>
       <c r="BP165" s="23"/>
     </row>
-    <row r="166" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN166" s="23"/>
       <c r="BO166" s="23"/>
       <c r="BP166" s="23"/>
     </row>
-    <row r="167" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D167" s="2" t="str" cm="1">
         <f t="array" ref="D167">Common_SourceData.Common_SourceData_EFleach_Title()</f>
         <v>Emission factor for nitrogen leaching and runoff</v>
@@ -19099,7 +19054,7 @@
       <c r="BO167" s="23"/>
       <c r="BP167" s="23"/>
     </row>
-    <row r="168" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D168" s="18" t="str" cm="1">
         <f t="array" ref="D168">Common_SourceData.Common_SourceData_EFleach_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
@@ -19108,7 +19063,7 @@
       <c r="BO168" s="23"/>
       <c r="BP168" s="23"/>
     </row>
-    <row r="169" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D169" s="18" t="str" cm="1">
         <f t="array" ref="D169">Common_SourceData.Common_SourceData_EFleach_NIRReference()</f>
         <v>National Inventory Report Volume 1: Equation 3.D.B_10</v>
@@ -19117,7 +19072,7 @@
       <c r="BO169" s="23"/>
       <c r="BP169" s="23"/>
     </row>
-    <row r="170" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D170" s="1" t="str" cm="1">
         <f t="array" ref="D170:E170">Common_SourceData.Common_SourceData_EFleach_Data()</f>
         <v>EFleach</v>
@@ -19129,17 +19084,17 @@
       <c r="BO170" s="23"/>
       <c r="BP170" s="23"/>
     </row>
-    <row r="171" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN171" s="23"/>
       <c r="BO171" s="23"/>
       <c r="BP171" s="23"/>
     </row>
-    <row r="172" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN172" s="23"/>
       <c r="BO172" s="23"/>
       <c r="BP172" s="23"/>
     </row>
-    <row r="173" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D173" s="2" t="str" cm="1">
         <f t="array" ref="D173">Common_SourceData.Common_SourceData_DensityOfMethane_Title()</f>
         <v>p = density of methane</v>
@@ -19148,7 +19103,7 @@
       <c r="BO173" s="23"/>
       <c r="BP173" s="23"/>
     </row>
-    <row r="174" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D174" s="18" t="str" cm="1">
         <f t="array" ref="D174">Common_SourceData.Common_SourceData_DensityOfMethane_Source()</f>
         <v>National Inventory Report 2023 Volume 1: Equations 3.B.1a_2, 3.B.1c_2, 3.B.3_1, 3.B.4g_2</v>
@@ -19157,7 +19112,7 @@
       <c r="BO174" s="23"/>
       <c r="BP174" s="23"/>
     </row>
-    <row r="175" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D175" s="1" cm="1">
         <f t="array" ref="D175">Common_SourceData.Common_SourceData_DensityOfMethane_Data()</f>
         <v>0.6784</v>
@@ -19170,17 +19125,17 @@
       <c r="BO175" s="23"/>
       <c r="BP175" s="23"/>
     </row>
-    <row r="176" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN176" s="23"/>
       <c r="BO176" s="23"/>
       <c r="BP176" s="23"/>
     </row>
-    <row r="177" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN177" s="23"/>
       <c r="BO177" s="23"/>
       <c r="BP177" s="23"/>
     </row>
-    <row r="178" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D178" s="2" t="str" cm="1">
         <f t="array" ref="D178">Common_SourceData.Common_SourceData_EFN2O_Title()</f>
         <v>Nitrous oxide emission factors for inorganic fertiliser application</v>
@@ -19189,7 +19144,7 @@
       <c r="BO178" s="23"/>
       <c r="BP178" s="23"/>
     </row>
-    <row r="179" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D179" s="18" t="str" cm="1">
         <f t="array" ref="D179">Common_SourceData.Common_SourceData_EFN2O_Source()</f>
         <v>VEERG 2026: Table A.2.2.1</v>
@@ -19198,39 +19153,39 @@
       <c r="BO179" s="23"/>
       <c r="BP179" s="23"/>
     </row>
-    <row r="180" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D180" s="10" t="str" cm="1">
         <f t="array" ref="D180">Common_SourceData.Common_SourceData_EFN2O_Unit()</f>
         <v>(kg N2O-N / kg N</v>
       </c>
     </row>
-    <row r="181" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D181" s="27" t="str" cm="1">
         <f t="array" ref="D181:D185">Common_SourceData.Common_SourceData_EFN2O_Variation()</f>
         <v>VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="182" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D182" s="27" t="str">
         <v>Removed duplicate 'Aquaculture' row.</v>
       </c>
     </row>
-    <row r="183" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D183" s="27" t="str">
         <v>Removed asterisks to aid lookup.</v>
       </c>
     </row>
-    <row r="184" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D184" s="27" t="str">
         <v>Added 'production system only', 'rainfall zone' and 'irrigation method' columns to aid lookup.</v>
       </c>
     </row>
-    <row r="185" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D185" s="27" t="str">
         <v>Duplicated 'non-irrigated pasture' row with same EF for low and high rainfall zones to aid lookup.</v>
       </c>
     </row>
-    <row r="186" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D186" s="21" t="s">
         <v>61</v>
       </c>
@@ -19247,7 +19202,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="187" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D187" s="21" t="str" cm="1">
         <f t="array" ref="D187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Irrigated pasture</v>
@@ -19269,7 +19224,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="188" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D188" s="21" t="str" cm="1">
         <f t="array" ref="D188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Irrigated crop</v>
@@ -19291,7 +19246,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="189" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D189" s="21" t="str" cm="1">
         <f t="array" ref="D189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated pasture</v>
@@ -19313,7 +19268,7 @@
         <v>Low rainfall</v>
       </c>
     </row>
-    <row r="190" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D190" s="21" t="str" cm="1">
         <f t="array" ref="D190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated pasture</v>
@@ -19335,7 +19290,7 @@
         <v>High rainfall</v>
       </c>
     </row>
-    <row r="191" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D191" s="21" t="str" cm="1">
         <f t="array" ref="D191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated crop (low rainfall)</v>
@@ -19357,7 +19312,7 @@
         <v>Low rainfall</v>
       </c>
     </row>
-    <row r="192" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D192" s="21" t="str" cm="1">
         <f t="array" ref="D192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated crop (high rainfall)</v>
@@ -19379,7 +19334,7 @@
         <v>High rainfall</v>
       </c>
     </row>
-    <row r="193" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D193" s="21" t="str" cm="1">
         <f t="array" ref="D193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Sugar</v>
@@ -19401,7 +19356,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="194" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D194" s="21" t="str" cm="1">
         <f t="array" ref="D194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Cotton</v>
@@ -19423,7 +19378,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="195" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D195" s="21" t="str" cm="1">
         <f t="array" ref="D195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Horticultural crops</v>
@@ -19445,7 +19400,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="196" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D196" s="21" t="str" cm="1">
         <f t="array" ref="D196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Rice (continuous flooding)</v>
@@ -19467,7 +19422,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="197" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="197" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D197" s="21" t="str" cm="1">
         <f t="array" ref="D197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Rice (single and multiple drainage, or alternate wetting and drying)</v>
@@ -19489,7 +19444,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="198" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="198" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D198" s="21" t="str" cm="1">
         <f t="array" ref="D198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Aquaculture</v>
@@ -19511,7 +19466,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="199" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="199" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D199" s="21" t="str" cm="1">
         <f t="array" ref="D199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Forestry</v>
@@ -19533,31 +19488,31 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="202" spans="4:8" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="202" spans="4:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D202" s="2" t="str" cm="1">
         <f t="array" ref="D202">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Title()</f>
         <v>Emission factor for urine and dung deposited on pasture, range or paddock</v>
       </c>
     </row>
-    <row r="203" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="203" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D203" s="18" t="str" cm="1">
         <f t="array" ref="D203">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Source()</f>
         <v>VEERG 2026: Table A.2.2.2</v>
       </c>
     </row>
-    <row r="204" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="204" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D204" s="27" t="str" cm="1">
         <f t="array" ref="D204">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Variation()</f>
         <v>VARIATION FROM SOURCE DATA: Changed 'Dry climate zones' to singular 'Dry climate zone' to aid lookup.</v>
       </c>
     </row>
-    <row r="205" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="205" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D205" s="10" t="str" cm="1">
         <f t="array" ref="D205">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Unit()</f>
         <v>kg N2O - N / kg N</v>
       </c>
     </row>
-    <row r="206" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="206" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D206" s="21" t="s">
         <v>32</v>
       </c>
@@ -19565,7 +19520,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="207" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="207" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D207" s="21" t="str" cm="1">
         <f t="array" ref="D207">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
         <v>Wet climate zone</v>
@@ -19575,7 +19530,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="208" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="208" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D208" s="1" t="str" cm="1">
         <f t="array" ref="D208">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
         <v>Dry climate zone</v>
@@ -19585,13 +19540,13 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="211" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D211" s="1" t="str" cm="1">
         <f t="array" ref="D211">Common_SourceData.Common_SourceData_MonthsToSeasons_Title()</f>
         <v>Months to Seasons Mapping</v>
       </c>
     </row>
-    <row r="212" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D212" s="21" t="s">
         <v>67</v>
       </c>
@@ -19599,7 +19554,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="213" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D213" s="21" t="str" cm="1">
         <f t="array" ref="D213">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>January</v>
@@ -19609,7 +19564,7 @@
         <v>Summer</v>
       </c>
     </row>
-    <row r="214" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D214" s="1" t="str" cm="1">
         <f t="array" ref="D214">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>February</v>
@@ -19619,7 +19574,7 @@
         <v>Summer</v>
       </c>
     </row>
-    <row r="215" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D215" s="1" t="str" cm="1">
         <f t="array" ref="D215">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>March</v>
@@ -19629,7 +19584,7 @@
         <v>Autumn</v>
       </c>
     </row>
-    <row r="216" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D216" s="1" t="str" cm="1">
         <f t="array" ref="D216">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>April</v>
@@ -19639,7 +19594,7 @@
         <v>Autumn</v>
       </c>
     </row>
-    <row r="217" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D217" s="1" t="str" cm="1">
         <f t="array" ref="D217">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>May</v>
@@ -19649,7 +19604,7 @@
         <v>Autumn</v>
       </c>
     </row>
-    <row r="218" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D218" s="1" t="str" cm="1">
         <f t="array" ref="D218">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>June</v>
@@ -19659,7 +19614,7 @@
         <v>Winter</v>
       </c>
     </row>
-    <row r="219" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D219" s="1" t="str" cm="1">
         <f t="array" ref="D219">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>July</v>
@@ -19669,7 +19624,7 @@
         <v>Winter</v>
       </c>
     </row>
-    <row r="220" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D220" s="1" t="str" cm="1">
         <f t="array" ref="D220">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>August</v>
@@ -19679,7 +19634,7 @@
         <v>Winter</v>
       </c>
     </row>
-    <row r="221" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="221" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D221" s="1" t="str" cm="1">
         <f t="array" ref="D221">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>September</v>
@@ -19689,7 +19644,7 @@
         <v>Spring</v>
       </c>
     </row>
-    <row r="222" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="222" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D222" s="1" t="str" cm="1">
         <f t="array" ref="D222">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>October</v>
@@ -19699,7 +19654,7 @@
         <v>Spring</v>
       </c>
     </row>
-    <row r="223" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="223" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D223" s="1" t="str" cm="1">
         <f t="array" ref="D223">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>November</v>
@@ -19709,7 +19664,7 @@
         <v>Spring</v>
       </c>
     </row>
-    <row r="224" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="224" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D224" s="1" t="str" cm="1">
         <f t="array" ref="D224">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>December</v>
@@ -19719,25 +19674,25 @@
         <v>Summer</v>
       </c>
     </row>
-    <row r="227" spans="4:19" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="227" spans="4:19" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D227" s="2" t="str" cm="1">
         <f t="array" ref="D227">Common_SourceData.Common_SourceData_MCFTemperatureZone_Title()</f>
         <v>Manure Management – Methane conversion factor per temperature zone (fraction) (MCFim)</v>
       </c>
     </row>
-    <row r="228" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="228" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D228" s="18" t="str" cm="1">
         <f t="array" ref="D228">Common_SourceData.Common_SourceData_MCFTemperatureZone_Source()</f>
         <v>VEERG 2026: Table A.1.8.1</v>
       </c>
     </row>
-    <row r="229" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="229" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D229" s="27" t="str" cm="1">
         <f t="array" ref="D229">Common_SourceData.Common_SourceData_MCFTemperatureZone_Variation()</f>
         <v>VARIATION FROM SOURCE: Added row of NIR MMA definitions to aid lookup. Duplicated 'Poultry with and without litter' column with separate NIR definitions to aid lookup. Added 'MAT raw' column to allow lookup of numbers.</v>
       </c>
     </row>
-    <row r="231" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="231" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D231" s="21" t="s">
         <v>69</v>
       </c>
@@ -19787,7 +19742,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="232" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="232" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D232" s="21" t="str" cm="1">
         <f t="array" ref="D232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -19853,7 +19808,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="233" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="233" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D233" s="1" t="str" cm="1">
         <f t="array" ref="D233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -19919,7 +19874,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="234" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="234" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D234" s="1" t="str" cm="1">
         <f t="array" ref="D234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -19985,7 +19940,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="235" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="235" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D235" s="1" t="str" cm="1">
         <f t="array" ref="D235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -20051,7 +20006,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="236" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="236" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D236" s="1" t="str" cm="1">
         <f t="array" ref="D236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -20117,7 +20072,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="237" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="237" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D237" s="1" t="str" cm="1">
         <f t="array" ref="D237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20183,7 +20138,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="238" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="238" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D238" s="1" t="str" cm="1">
         <f t="array" ref="D238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20249,7 +20204,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="239" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="239" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D239" s="1" t="str" cm="1">
         <f t="array" ref="D239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20315,7 +20270,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="240" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="240" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D240" s="1" t="str" cm="1">
         <f t="array" ref="D240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20381,7 +20336,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="241" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="241" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D241" s="1" t="str" cm="1">
         <f t="array" ref="D241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20447,7 +20402,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="242" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="242" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D242" s="1" t="str" cm="1">
         <f t="array" ref="D242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20513,7 +20468,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="243" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="243" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D243" s="1" t="str" cm="1">
         <f t="array" ref="D243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20579,7 +20534,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="244" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="244" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D244" s="1" t="str" cm="1">
         <f t="array" ref="D244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20645,7 +20600,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="245" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="245" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D245" s="1" t="str" cm="1">
         <f t="array" ref="D245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20711,7 +20666,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="246" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="246" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D246" s="1" t="str" cm="1">
         <f t="array" ref="D246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20777,7 +20732,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="247" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="247" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D247" s="1" t="str" cm="1">
         <f t="array" ref="D247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20843,7 +20798,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="248" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="248" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D248" s="1" t="str" cm="1">
         <f t="array" ref="D248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
@@ -20909,7 +20864,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="249" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="249" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D249" s="1" t="str" cm="1">
         <f t="array" ref="D249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
@@ -20975,7 +20930,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="250" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="250" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D250" s="1" t="str" cm="1">
         <f t="array" ref="D250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
@@ -21041,31 +20996,31 @@
         <v>28</v>
       </c>
     </row>
-    <row r="253" spans="4:19" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="253" spans="4:19" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D253" s="2" t="str" cm="1">
         <f t="array" ref="D253">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Title()</f>
         <v>Emission factor for organic fertiliser and crop residues returned to the soil</v>
       </c>
     </row>
-    <row r="254" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="254" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D254" s="18" t="str" cm="1">
         <f t="array" ref="D254">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Source()</f>
         <v>VEERG 2026: Table A.2.1.4</v>
       </c>
     </row>
-    <row r="255" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="255" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D255" s="1" t="str" cm="1">
         <f t="array" ref="D255">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Variable()</f>
         <v>EFNi &amp; EFN2Oi</v>
       </c>
     </row>
-    <row r="256" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="256" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D256" s="10" t="str" cm="1">
         <f t="array" ref="D256">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Unit()</f>
         <v>kg N2O - N / kg N</v>
       </c>
     </row>
-    <row r="257" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="257" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D257" s="21" t="s">
         <v>85</v>
       </c>
@@ -21073,7 +21028,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="258" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="258" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D258" s="21" t="str" cm="1">
         <f t="array" ref="D258">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>Wet climate zone</v>
@@ -21083,7 +21038,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="259" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="259" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D259" s="1" t="str" cm="1">
         <f t="array" ref="D259">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>Dry climate zone</v>
@@ -21093,17 +21048,17 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="263" spans="4:66" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="263" spans="4:66" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D263" s="2" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="264" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="264" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D264" s="1" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="265" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="265" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D265" s="21" t="s">
         <v>234</v>
       </c>
@@ -21119,7 +21074,7 @@
       <c r="V265" s="1"/>
       <c r="BN265" s="23"/>
     </row>
-    <row r="266" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="266" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D266" s="21" t="s">
         <v>235</v>
       </c>
@@ -21135,7 +21090,7 @@
       <c r="V266" s="1"/>
       <c r="BN266" s="23"/>
     </row>
-    <row r="267" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="267" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D267" s="21" t="s">
         <v>236</v>
       </c>
@@ -21151,7 +21106,7 @@
       <c r="V267" s="1"/>
       <c r="BN267" s="23"/>
     </row>
-    <row r="268" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="268" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D268" s="21" t="s">
         <v>237</v>
       </c>
@@ -21167,7 +21122,7 @@
       <c r="V268" s="1"/>
       <c r="BN268" s="23"/>
     </row>
-    <row r="269" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="269" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D269" s="21" t="s">
         <v>238</v>
       </c>
@@ -21183,7 +21138,7 @@
       <c r="V269" s="1"/>
       <c r="BN269" s="23"/>
     </row>
-    <row r="270" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="270" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D270" s="21" t="s">
         <v>239</v>
       </c>
@@ -21199,12 +21154,12 @@
       <c r="V270" s="1"/>
       <c r="BN270" s="23"/>
     </row>
-    <row r="273" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="273" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D273" s="1" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="274" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="274" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D274" s="21" t="s">
         <v>234</v>
       </c>
@@ -21220,7 +21175,7 @@
       <c r="V274" s="1"/>
       <c r="BN274" s="23"/>
     </row>
-    <row r="275" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="275" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D275" s="21" t="s">
         <v>240</v>
       </c>
@@ -21236,7 +21191,7 @@
       <c r="V275" s="1"/>
       <c r="BN275" s="23"/>
     </row>
-    <row r="276" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="276" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D276" s="21" t="s">
         <v>241</v>
       </c>
@@ -21252,7 +21207,7 @@
       <c r="V276" s="1"/>
       <c r="BN276" s="23"/>
     </row>
-    <row r="277" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="277" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D277" s="21" t="s">
         <v>242</v>
       </c>
@@ -21268,7 +21223,7 @@
       <c r="V277" s="1"/>
       <c r="BN277" s="23"/>
     </row>
-    <row r="278" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="278" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D278" s="21" t="s">
         <v>243</v>
       </c>
@@ -21284,7 +21239,7 @@
       <c r="V278" s="1"/>
       <c r="BN278" s="23"/>
     </row>
-    <row r="279" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="279" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D279" s="21" t="s">
         <v>244</v>
       </c>
@@ -21300,12 +21255,12 @@
       <c r="V279" s="1"/>
       <c r="BN279" s="23"/>
     </row>
-    <row r="282" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="282" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D282" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="283" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="283" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D283" s="21" t="s">
         <v>234</v>
       </c>
@@ -21321,7 +21276,7 @@
       <c r="V283" s="1"/>
       <c r="BN283" s="23"/>
     </row>
-    <row r="284" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="284" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D284" s="21" t="s">
         <v>245</v>
       </c>
@@ -21337,7 +21292,7 @@
       <c r="V284" s="1"/>
       <c r="BN284" s="23"/>
     </row>
-    <row r="285" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="285" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D285" s="21" t="s">
         <v>246</v>
       </c>
@@ -21353,7 +21308,7 @@
       <c r="V285" s="1"/>
       <c r="BN285" s="23"/>
     </row>
-    <row r="286" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="286" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D286" s="21" t="s">
         <v>247</v>
       </c>
@@ -21369,7 +21324,7 @@
       <c r="V286" s="1"/>
       <c r="BN286" s="23"/>
     </row>
-    <row r="287" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="287" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D287" s="21" t="s">
         <v>248</v>
       </c>
@@ -21385,7 +21340,7 @@
       <c r="V287" s="1"/>
       <c r="BN287" s="23"/>
     </row>
-    <row r="288" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="288" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D288" s="21" t="s">
         <v>249</v>
       </c>
@@ -21401,12 +21356,12 @@
       <c r="V288" s="1"/>
       <c r="BN288" s="23"/>
     </row>
-    <row r="291" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="291" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D291" s="1" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="292" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="292" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D292" s="21" t="s">
         <v>234</v>
       </c>
@@ -21422,7 +21377,7 @@
       <c r="V292" s="1"/>
       <c r="BN292" s="23"/>
     </row>
-    <row r="293" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="293" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D293" s="21" t="s">
         <v>250</v>
       </c>
@@ -21438,7 +21393,7 @@
       <c r="V293" s="1"/>
       <c r="BN293" s="23"/>
     </row>
-    <row r="294" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="294" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D294" s="21" t="s">
         <v>251</v>
       </c>
@@ -21454,7 +21409,7 @@
       <c r="V294" s="1"/>
       <c r="BN294" s="23"/>
     </row>
-    <row r="295" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="295" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D295" s="21" t="s">
         <v>252</v>
       </c>
@@ -21470,7 +21425,7 @@
       <c r="V295" s="1"/>
       <c r="BN295" s="23"/>
     </row>
-    <row r="296" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="296" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D296" s="21" t="s">
         <v>253</v>
       </c>
@@ -21486,7 +21441,7 @@
       <c r="V296" s="1"/>
       <c r="BN296" s="23"/>
     </row>
-    <row r="297" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="297" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D297" s="21" t="s">
         <v>254</v>
       </c>
